--- a/data/LanguageFamily.xlsx
+++ b/data/LanguageFamily.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/psav050/Documents/GitHub/sync-coop-song-speech/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16A69E3-8D19-3949-9EAF-6851B2B34EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85453AAF-0113-4B4D-AF16-E2F14787FD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="940" windowWidth="26720" windowHeight="13600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11400" yWindow="3760" windowWidth="18840" windowHeight="11740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Many Voices 2 languages" sheetId="7" r:id="rId1"/>
@@ -481,14 +481,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -803,11 +803,11 @@
       <c r="G4" s="9">
         <v>33</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:44" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
@@ -821,7 +821,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="41" t="s">
@@ -849,18 +849,18 @@
       <c r="G6" s="10">
         <v>34</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
     </row>
     <row r="7" spans="1:44" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="32">
         <v>19</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="28">
@@ -1028,7 +1028,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15"/>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="28">
@@ -1054,7 +1054,7 @@
         <v>39</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15"/>
@@ -1066,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="32">
@@ -1080,7 +1080,7 @@
         <v>40</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15"/>
@@ -1092,7 +1092,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="28">
@@ -1118,7 +1118,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="28">
@@ -1142,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="28">
@@ -1164,7 +1164,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="28">
@@ -1188,7 +1188,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="28">
@@ -1268,4 +1268,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b75eb9d1-7479-4f8a-9240-cc5b19dbbc64}" enabled="1" method="Standard" siteId="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>